--- a/redirect/glavis-recruit-url-redirect-sheet.xlsx
+++ b/redirect/glavis-recruit-url-redirect-sheet.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ご記入方法" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採用サイトURL一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選択肢" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'採用サイトURL一覧'!$A$3:$H$63</definedName>
@@ -2688,9 +2689,44 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F4:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ご回答" error="プルダウンからお選びください" type="list">
-      <formula1>"案の通りでOK,変更したい（G列にご記入）,このページは廃止（採用トップへ）"</formula1>
+      <formula1>=選択肢!$A$1:$A$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>案の通りでOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>変更したい（G列にご記入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>このページは廃止（採用トップへ）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/redirect/glavis-recruit-url-redirect-sheet.xlsx
+++ b/redirect/glavis-recruit-url-redirect-sheet.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B22"/>
+  <dimension ref="B2:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -552,14 +552,14 @@
     <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>採用サイトURL 遷移先ご回答シート</t>
+          <t>採用サイトURL 一覧（301リダイレクト設定内容）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>株式会社ITLINE／2026年8月9日　ご回答期限：2026年9月5日（金）</t>
+          <t>株式会社ITLINE／2026年8月9日　ご確認は任意です（例外がある場合のみご指定ください）</t>
         </is>
       </c>
     </row>
@@ -583,98 +583,112 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>全60ページ分の転送先はITLINEにて機械的に割り当て済みです（E列・薄緑）。内容をご確認いただき、例外だけご指定ください。</t>
+          <t>全60ページ分の転送先はITLINEにて機械的に設定いたします（E列・薄緑）。本シートはその設定内容をご確認いただくための資料です。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>移設実施の際に、設定したリダイレクトの一覧をあらためてご提出し、設定済みである旨をご報告いたします。事前のご回答は不要です。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ご記入いただくのは F列（薄黄）だけです</t>
-        </is>
-      </c>
+      <c r="B9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>・案の通りでよい行 → そのまま（初期値「案の通りでOK」）。何もしなくて結構です。</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>例外をご指定いただく場合のみ、F列（薄黄）をご変更ください</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>・転送先を変えたい行 → F列で「変更したい」を選び、G列に転送先URLをご記入ください。</t>
+          <t>・案の通りでよい行 → そのまま（初期値「案の通りでOK」）。何もしなくて結構です。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>・転送先を変えたい行 → F列で「変更したい」を選び、G列に転送先URLをご記入ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>・新サイトに残さないページ → F列で「このページは廃止（採用トップへ）」を選択してください。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="3" t="n"/>
-    </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>特にご確認いただきたい点</t>
-        </is>
-      </c>
+      <c r="B14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>・Web広告のリンク先（LP）に使用しているURLがあれば、その行の転送先を優先的にご確認ください。</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ご参考：特にご確認いただくとよい点</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="5" t="inlineStr">
         <is>
+          <t>・Web広告のリンク先（LP）に使用しているURLがあれば、その行の転送先をご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
           <t>・掲載終了予定の求人（キャリア採用の各ページ）は「廃止」をご選択いただければ、求人一覧ページへ転送します。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="n"/>
-    </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>ご返送方法</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>ご記入後、このファイルをメールに添付し、下記までご返送ください。</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ご連絡方法（例外がある場合のみ）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>宛先：tsutomu.kado@mocamoco.com（加堂）／ kodama@itline.co.jp（小玉）</t>
+          <t>このファイルをメールに添付し、下記までご返送ください。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>件名：【GLAVIS】採用サイトURL遷移先のご回答</t>
+          <t>該当箇所が少なければ、本文に「○○のページは△△へ」とご記入いただくだけでも結構です。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>宛先：tsutomu.kado@mocamoco.com（加堂）／ kodama@itline.co.jp（小玉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>件名：【GLAVIS】採用サイトURL遷移先のご指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Teams のプライベートチャットへの添付でも結構です。</t>
         </is>
@@ -707,14 +721,14 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>採用サイトURL一覧（全60件）　ご記入は F列・G列のみ</t>
+          <t>採用サイトURL一覧（全60件）　ご記入は任意（F列・G列のみ）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>E列＝転送先のITLINE案（確認用）。F列の初期値は「案の通りでOK」です。例外の行だけ変更してください。</t>
+          <t>E列＝ITLINEにて設定する転送先。F列の初期値は「案の通りでOK」です。例外がある行のみ変更してください（ご返送は任意です）。</t>
         </is>
       </c>
     </row>
